--- a/1.Uracils/5aminouracil/5aminouracilA/5aminouracilA.xlsx
+++ b/1.Uracils/5aminouracil/5aminouracilA/5aminouracilA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lspri\UCL Dropbox\Louise Price\Temporary Folder for Github\Uracils\5aminouracilA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lspri\Documents\GitHub\CPOSS_Database\1.Uracils\5aminouracil\5aminouracilA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EF8E18B-FA78-49CE-A5ED-CB9CA8F57914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{842A0748-9C22-4C06-8E80-1C9486814292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BDE3A0E-2FAE-423B-9692-F0CED10A34BC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{498B71B1-4664-40C5-8709-5338470A506D}"/>
   </bookViews>
   <sheets>
     <sheet name="5aminouracilA_forxls" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="143">
   <si>
     <t>Filename</t>
   </si>
@@ -43,409 +43,412 @@
     <t>Experimental Info</t>
   </si>
   <si>
-    <t>UCLAUR_opt_au26</t>
+    <t>JAVRIM_opt_au26</t>
   </si>
   <si>
     <t>Pna21</t>
   </si>
   <si>
-    <t>Exp unpublished</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_am91</t>
+    <t>JAVRIM (Form I)</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_eo1</t>
+  </si>
+  <si>
+    <t>JAVRIM (Form IE)</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_am91</t>
   </si>
   <si>
     <t>P21/n</t>
   </si>
   <si>
-    <t>UCLAUR_opt_am131</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_am57</t>
+    <t>JAVRIM_opt_am131</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_am57</t>
   </si>
   <si>
     <t>P21/c</t>
   </si>
   <si>
-    <t>UCLAUR_opt_fc35</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_bd74</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_am76</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_av94</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ca121</t>
+    <t>JAVRIM_opt_fc35</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_bd74</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_am76</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_av94</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ca121</t>
   </si>
   <si>
     <t>P-1</t>
   </si>
   <si>
-    <t>UCLAUR_opt_ca53</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ap73</t>
+    <t>JAVRIM_opt_ca53</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ap73</t>
   </si>
   <si>
     <t>P21212</t>
   </si>
   <si>
-    <t>UCLAUR_opt_ah11</t>
+    <t>JAVRIM_opt_ah11</t>
   </si>
   <si>
     <t>P21</t>
   </si>
   <si>
-    <t>UCLAUR_opt_bh65</t>
+    <t>JAVRIM_opt_bh65</t>
   </si>
   <si>
     <t>Pa</t>
   </si>
   <si>
-    <t>UCLAUR_opt_aq95</t>
+    <t>JAVRIM_opt_aq95</t>
   </si>
   <si>
     <t>P212121</t>
   </si>
   <si>
-    <t>UCLAUR_opt_aw62</t>
+    <t>JAVRIM_opt_aw62</t>
   </si>
   <si>
     <t>Pba2</t>
   </si>
   <si>
-    <t>UCLAUR_opt_aq69</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_dc75</t>
+    <t>JAVRIM_opt_aq69</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_dc75</t>
   </si>
   <si>
     <t>C2/c</t>
   </si>
   <si>
-    <t>UCLAUR_opt_ca45</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_af61</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fc72</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_dc80</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_bj109</t>
+    <t>JAVRIM_opt_ca45</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_af61</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fc72</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_dc80</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_bj109</t>
   </si>
   <si>
     <t>P1</t>
   </si>
   <si>
-    <t>UCLAUR_opt_ai56</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_bh14</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ap10</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_aq25</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ak62</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ai51</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_aj79</t>
+    <t>JAVRIM_opt_ai56</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_bh14</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ap10</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_aq25</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ak62</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ai51</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_aj79</t>
   </si>
   <si>
     <t>Pc</t>
   </si>
   <si>
-    <t>UCLAUR_opt_ce48</t>
+    <t>JAVRIM_opt_ce48</t>
   </si>
   <si>
     <t>P2111</t>
   </si>
   <si>
-    <t>UCLAUR_opt_fc6</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ak46</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_de111</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_am19</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_av80</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_cd83</t>
+    <t>JAVRIM_opt_fc6</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ak46</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_de111</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_am19</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_av80</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_cd83</t>
   </si>
   <si>
     <t>Pbcn</t>
   </si>
   <si>
-    <t>UCLAUR_opt_de73</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ak24</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fc77</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ak88</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_am125</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fa80</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ab94</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_am43</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_al46</t>
+    <t>JAVRIM_opt_de73</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ak24</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fc77</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ak88</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_am125</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fa80</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ab94</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_am43</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_al46</t>
   </si>
   <si>
     <t>P2/c</t>
   </si>
   <si>
-    <t>UCLAUR_opt_de25</t>
+    <t>JAVRIM_opt_de25</t>
   </si>
   <si>
     <t>C-1</t>
   </si>
   <si>
-    <t>UCLAUR_opt_cc126</t>
+    <t>JAVRIM_opt_cc126</t>
   </si>
   <si>
     <t>Pbc21</t>
   </si>
   <si>
-    <t>UCLAUR_opt_fa48</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_eo1</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fc45</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ai110</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_al66</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_al51</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_aj13</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_cc32</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fa95</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fc13</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ay104</t>
+    <t>JAVRIM_opt_fa48</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fc45</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ai110</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_al66</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_al51</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_aj13</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_cc32</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fa95</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fc13</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ay104</t>
   </si>
   <si>
     <t>Pca21</t>
   </si>
   <si>
-    <t>UCLAUR_opt_de76</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_av71</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_aj73</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_al81</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ay78</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fa82</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ce35</t>
+    <t>JAVRIM_opt_de76</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_av71</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_aj73</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_al81</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ay78</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fa82</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ce35</t>
   </si>
   <si>
     <t>P21cn</t>
   </si>
   <si>
-    <t>UCLAUR_opt_bh7</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_bb50</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_bb65</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ce76</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_aq54</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_dd65</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ab75</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fc40</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_af14</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fa47</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ba16</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_dc109</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ai114</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_dd12</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_dc30</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_bh47</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ai44</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_db87</t>
+    <t>JAVRIM_opt_bh7</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_bb50</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_bb65</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ce76</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_aq54</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_dd65</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ab75</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fc40</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_af14</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fa47</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ba16</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_dc109</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ai114</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_dd12</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_dc30</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_bh47</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ai44</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_db87</t>
   </si>
   <si>
     <t>C2</t>
   </si>
   <si>
-    <t>UCLAUR_opt_de13</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_dc15</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_au77</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ak87</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ak54</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_cd124</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fa24</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_aj44</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ca63</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_al112</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ai35</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_dc81</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ca21</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_de113</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_am47</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fa49</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fc8</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_fc89</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_af50</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_am48</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_am44</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_de115</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_db74</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_cc100</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_af76</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_av21</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_ca91</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_av2</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_bj58</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_am45</t>
-  </si>
-  <si>
-    <t>UCLAUR_opt_bb36</t>
+    <t>JAVRIM_opt_de13</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_dc15</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_au77</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ak87</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ak54</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_cd124</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fa24</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_aj44</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ca63</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_al112</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ai35</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_dc81</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ca21</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_de113</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_am47</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fa49</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fc8</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_fc89</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_af50</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_am48</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_am44</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_de115</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_db74</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_cc100</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_af76</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_av21</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_ca91</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_av2</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_bj58</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_am45</t>
+  </si>
+  <si>
+    <t>JAVRIM_opt_bb36</t>
   </si>
 </sst>
 </file>
@@ -1305,7 +1308,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB39AE5-40FD-4AEA-BD23-BA96630D4AE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD41D2EC-B8DD-4FAD-8111-90A2ADAD45F6}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1360,18 +1364,21 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>1.658944</v>
+        <v>1.6531</v>
       </c>
       <c r="C3">
-        <v>-128.161</v>
+        <v>-117.024</v>
       </c>
       <c r="D3">
-        <v>-142.333</v>
+        <v>-117.024</v>
       </c>
       <c r="E3">
-        <v>0.76035699999999995</v>
+        <v>0.76947699999999997</v>
       </c>
       <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1380,39 +1387,39 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>1.691295</v>
+        <v>1.658944</v>
       </c>
       <c r="C4">
-        <v>-125.633</v>
+        <v>-128.161</v>
       </c>
       <c r="D4">
-        <v>-139.035</v>
+        <v>-142.333</v>
       </c>
       <c r="E4">
-        <v>0.77914099999999997</v>
+        <v>0.76035699999999995</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>1.691295</v>
+      </c>
+      <c r="C5">
+        <v>-125.633</v>
+      </c>
+      <c r="D5">
+        <v>-139.035</v>
+      </c>
+      <c r="E5">
+        <v>0.77914099999999997</v>
+      </c>
+      <c r="F5" t="s">
         <v>13</v>
-      </c>
-      <c r="B5">
-        <v>1.676698</v>
-      </c>
-      <c r="C5">
-        <v>-125.508</v>
-      </c>
-      <c r="D5">
-        <v>-139.95099999999999</v>
-      </c>
-      <c r="E5">
-        <v>0.77546899999999996</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1420,99 +1427,99 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>1.65402</v>
+        <v>1.676698</v>
       </c>
       <c r="C6">
-        <v>-125.13800000000001</v>
+        <v>-125.508</v>
       </c>
       <c r="D6">
-        <v>-142.12899999999999</v>
+        <v>-139.95099999999999</v>
       </c>
       <c r="E6">
-        <v>0.76299300000000003</v>
+        <v>0.77546899999999996</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
-        <v>1.6331</v>
+        <v>1.65402</v>
       </c>
       <c r="C7">
-        <v>-123.86799999999999</v>
+        <v>-125.13800000000001</v>
       </c>
       <c r="D7">
-        <v>-141.375</v>
+        <v>-142.12899999999999</v>
       </c>
       <c r="E7">
-        <v>0.75297700000000001</v>
+        <v>0.76299300000000003</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>1.712491</v>
+        <v>1.6331</v>
       </c>
       <c r="C8">
-        <v>-122.685</v>
+        <v>-123.86799999999999</v>
       </c>
       <c r="D8">
-        <v>-137.64699999999999</v>
+        <v>-141.375</v>
       </c>
       <c r="E8">
-        <v>0.79638799999999998</v>
+        <v>0.75297700000000001</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
-        <v>1.62374</v>
+        <v>1.712491</v>
       </c>
       <c r="C9">
-        <v>-122.205</v>
+        <v>-122.685</v>
       </c>
       <c r="D9">
-        <v>-138.26499999999999</v>
+        <v>-137.64699999999999</v>
       </c>
       <c r="E9">
-        <v>0.74717199999999995</v>
+        <v>0.79638799999999998</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
-        <v>1.725822</v>
+        <v>1.62374</v>
       </c>
       <c r="C10">
-        <v>-121.264</v>
+        <v>-122.205</v>
       </c>
       <c r="D10">
-        <v>-135.541</v>
+        <v>-138.26499999999999</v>
       </c>
       <c r="E10">
-        <v>0.80022300000000002</v>
+        <v>0.74717199999999995</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1520,39 +1527,39 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>1.7175069999999999</v>
+        <v>1.725822</v>
       </c>
       <c r="C11">
-        <v>-120.56699999999999</v>
+        <v>-121.264</v>
       </c>
       <c r="D11">
-        <v>-134.62299999999999</v>
+        <v>-135.541</v>
       </c>
       <c r="E11">
-        <v>0.79388400000000003</v>
+        <v>0.80022300000000002</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>1.7175069999999999</v>
+      </c>
+      <c r="C12">
+        <v>-120.56699999999999</v>
+      </c>
+      <c r="D12">
+        <v>-134.62299999999999</v>
+      </c>
+      <c r="E12">
+        <v>0.79388400000000003</v>
+      </c>
+      <c r="F12" t="s">
         <v>22</v>
-      </c>
-      <c r="B12">
-        <v>1.666785</v>
-      </c>
-      <c r="C12">
-        <v>-119.88800000000001</v>
-      </c>
-      <c r="D12">
-        <v>-135.142</v>
-      </c>
-      <c r="E12">
-        <v>0.76621499999999998</v>
-      </c>
-      <c r="F12" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1560,16 +1567,16 @@
         <v>24</v>
       </c>
       <c r="B13">
-        <v>1.619478</v>
+        <v>1.666785</v>
       </c>
       <c r="C13">
-        <v>-119.57299999999999</v>
+        <v>-119.88800000000001</v>
       </c>
       <c r="D13">
-        <v>-134.63</v>
+        <v>-135.142</v>
       </c>
       <c r="E13">
-        <v>0.75281900000000002</v>
+        <v>0.76621499999999998</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -1580,16 +1587,16 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>1.5803940000000001</v>
+        <v>1.619478</v>
       </c>
       <c r="C14">
-        <v>-119.494</v>
+        <v>-119.57299999999999</v>
       </c>
       <c r="D14">
-        <v>-136.70599999999999</v>
+        <v>-134.63</v>
       </c>
       <c r="E14">
-        <v>0.72639799999999999</v>
+        <v>0.75281900000000002</v>
       </c>
       <c r="F14" t="s">
         <v>27</v>
@@ -1600,16 +1607,16 @@
         <v>28</v>
       </c>
       <c r="B15">
-        <v>1.6511549999999999</v>
+        <v>1.5803940000000001</v>
       </c>
       <c r="C15">
-        <v>-119.43</v>
+        <v>-119.494</v>
       </c>
       <c r="D15">
-        <v>-136.84200000000001</v>
+        <v>-136.70599999999999</v>
       </c>
       <c r="E15">
-        <v>0.76351100000000005</v>
+        <v>0.72639799999999999</v>
       </c>
       <c r="F15" t="s">
         <v>29</v>
@@ -1620,16 +1627,16 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>1.644882</v>
+        <v>1.6511549999999999</v>
       </c>
       <c r="C16">
-        <v>-119.321</v>
+        <v>-119.43</v>
       </c>
       <c r="D16">
-        <v>-136.512</v>
+        <v>-136.84200000000001</v>
       </c>
       <c r="E16">
-        <v>0.76636499999999996</v>
+        <v>0.76351100000000005</v>
       </c>
       <c r="F16" t="s">
         <v>31</v>
@@ -1640,39 +1647,39 @@
         <v>32</v>
       </c>
       <c r="B17">
-        <v>1.6505650000000001</v>
+        <v>1.644882</v>
       </c>
       <c r="C17">
-        <v>-119.21899999999999</v>
+        <v>-119.321</v>
       </c>
       <c r="D17">
-        <v>-135.70599999999999</v>
+        <v>-136.512</v>
       </c>
       <c r="E17">
-        <v>0.76820999999999995</v>
+        <v>0.76636499999999996</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18">
-        <v>1.6959500000000001</v>
+        <v>1.6505650000000001</v>
       </c>
       <c r="C18">
-        <v>-119.057</v>
+        <v>-119.21899999999999</v>
       </c>
       <c r="D18">
-        <v>-133.96700000000001</v>
+        <v>-135.70599999999999</v>
       </c>
       <c r="E18">
-        <v>0.78467399999999998</v>
+        <v>0.76820999999999995</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1680,99 +1687,99 @@
         <v>35</v>
       </c>
       <c r="B19">
-        <v>1.7217389999999999</v>
+        <v>1.6959500000000001</v>
       </c>
       <c r="C19">
-        <v>-118.864</v>
+        <v>-119.057</v>
       </c>
       <c r="D19">
-        <v>-133.94300000000001</v>
+        <v>-133.96700000000001</v>
       </c>
       <c r="E19">
-        <v>0.78763899999999998</v>
+        <v>0.78467399999999998</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20">
-        <v>1.6428400000000001</v>
+        <v>1.7217389999999999</v>
       </c>
       <c r="C20">
-        <v>-118.801</v>
+        <v>-118.864</v>
       </c>
       <c r="D20">
-        <v>-135.709</v>
+        <v>-133.94300000000001</v>
       </c>
       <c r="E20">
-        <v>0.76020600000000005</v>
+        <v>0.78763899999999998</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21">
-        <v>1.6568179999999999</v>
+        <v>1.6428400000000001</v>
       </c>
       <c r="C21">
-        <v>-118.755</v>
+        <v>-118.801</v>
       </c>
       <c r="D21">
-        <v>-137.06</v>
+        <v>-135.709</v>
       </c>
       <c r="E21">
-        <v>0.77046000000000003</v>
+        <v>0.76020600000000005</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22">
-        <v>1.56165</v>
+        <v>1.6568179999999999</v>
       </c>
       <c r="C22">
-        <v>-118.623</v>
+        <v>-118.755</v>
       </c>
       <c r="D22">
-        <v>-135.935</v>
+        <v>-137.06</v>
       </c>
       <c r="E22">
-        <v>0.71622399999999997</v>
+        <v>0.77046000000000003</v>
       </c>
       <c r="F22" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23">
-        <v>1.6587719999999999</v>
+        <v>1.56165</v>
       </c>
       <c r="C23">
-        <v>-118.514</v>
+        <v>-118.623</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>-135.935</v>
       </c>
       <c r="E23">
-        <v>0.770482</v>
+        <v>0.71622399999999997</v>
       </c>
       <c r="F23" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1780,139 +1787,139 @@
         <v>41</v>
       </c>
       <c r="B24">
-        <v>1.7084170000000001</v>
+        <v>1.6587719999999999</v>
       </c>
       <c r="C24">
-        <v>-118.417</v>
+        <v>-118.514</v>
       </c>
       <c r="D24">
-        <v>-133.089</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>0.79002799999999995</v>
+        <v>0.770482</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25">
-        <v>1.6481250000000001</v>
+        <v>1.7084170000000001</v>
       </c>
       <c r="C25">
-        <v>-118.41500000000001</v>
+        <v>-118.417</v>
       </c>
       <c r="D25">
-        <v>-136.959</v>
+        <v>-133.089</v>
       </c>
       <c r="E25">
-        <v>0.76356400000000002</v>
+        <v>0.79002799999999995</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26">
-        <v>1.6267640000000001</v>
+        <v>1.6481250000000001</v>
       </c>
       <c r="C26">
-        <v>-118.248</v>
+        <v>-118.41500000000001</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>-136.959</v>
       </c>
       <c r="E26">
-        <v>0.75925200000000004</v>
+        <v>0.76356400000000002</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B27">
-        <v>1.6042829999999999</v>
+        <v>1.6267640000000001</v>
       </c>
       <c r="C27">
         <v>-118.248</v>
       </c>
       <c r="D27">
-        <v>-133.423</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0.738487</v>
+        <v>0.75925200000000004</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B28">
-        <v>1.6008610000000001</v>
+        <v>1.6042829999999999</v>
       </c>
       <c r="C28">
-        <v>-118.23699999999999</v>
+        <v>-118.248</v>
       </c>
       <c r="D28">
-        <v>-135.059</v>
+        <v>-133.423</v>
       </c>
       <c r="E28">
-        <v>0.73730600000000002</v>
+        <v>0.738487</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B29">
-        <v>1.6251180000000001</v>
+        <v>1.6008610000000001</v>
       </c>
       <c r="C29">
-        <v>-118.15900000000001</v>
+        <v>-118.23699999999999</v>
       </c>
       <c r="D29">
-        <v>-135.148</v>
+        <v>-135.059</v>
       </c>
       <c r="E29">
-        <v>0.74974300000000005</v>
+        <v>0.73730600000000002</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B30">
-        <v>1.633534</v>
+        <v>1.6251180000000001</v>
       </c>
       <c r="C30">
-        <v>-118.151</v>
+        <v>-118.15900000000001</v>
       </c>
       <c r="D30">
-        <v>-135.28299999999999</v>
+        <v>-135.148</v>
       </c>
       <c r="E30">
-        <v>0.75430399999999997</v>
+        <v>0.74974300000000005</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1920,16 +1927,16 @@
         <v>49</v>
       </c>
       <c r="B31">
-        <v>1.611661</v>
+        <v>1.633534</v>
       </c>
       <c r="C31">
-        <v>-118.078</v>
+        <v>-118.151</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>-135.28299999999999</v>
       </c>
       <c r="E31">
-        <v>0.742062</v>
+        <v>0.75430399999999997</v>
       </c>
       <c r="F31" t="s">
         <v>50</v>
@@ -1940,119 +1947,119 @@
         <v>51</v>
       </c>
       <c r="B32">
-        <v>1.7339119999999999</v>
+        <v>1.611661</v>
       </c>
       <c r="C32">
-        <v>-118.06399999999999</v>
+        <v>-118.078</v>
       </c>
       <c r="D32">
-        <v>-134.08000000000001</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>0.80080399999999996</v>
+        <v>0.742062</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B33">
-        <v>1.605</v>
+        <v>1.7339119999999999</v>
       </c>
       <c r="C33">
-        <v>-117.91800000000001</v>
+        <v>-118.06399999999999</v>
       </c>
       <c r="D33">
-        <v>-132.85499999999999</v>
+        <v>-134.08000000000001</v>
       </c>
       <c r="E33">
-        <v>0.73684099999999997</v>
+        <v>0.80080399999999996</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B34">
-        <v>1.6116299999999999</v>
+        <v>1.605</v>
       </c>
       <c r="C34">
-        <v>-117.789</v>
+        <v>-117.91800000000001</v>
       </c>
       <c r="D34">
-        <v>-134.67500000000001</v>
+        <v>-132.85499999999999</v>
       </c>
       <c r="E34">
-        <v>0.742811</v>
+        <v>0.73684099999999997</v>
       </c>
       <c r="F34" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B35">
-        <v>1.7358279999999999</v>
+        <v>1.6116299999999999</v>
       </c>
       <c r="C35">
-        <v>-117.621</v>
+        <v>-117.789</v>
       </c>
       <c r="D35">
-        <v>-133.023</v>
+        <v>-134.67500000000001</v>
       </c>
       <c r="E35">
-        <v>0.805454</v>
+        <v>0.742811</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B36">
-        <v>1.696099</v>
+        <v>1.7358279999999999</v>
       </c>
       <c r="C36">
-        <v>-117.581</v>
+        <v>-117.621</v>
       </c>
       <c r="D36">
-        <v>-147.58799999999999</v>
+        <v>-133.023</v>
       </c>
       <c r="E36">
-        <v>0.79302499999999998</v>
+        <v>0.805454</v>
       </c>
       <c r="F36" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B37">
-        <v>1.6896100000000001</v>
+        <v>1.696099</v>
       </c>
       <c r="C37">
         <v>-117.581</v>
       </c>
       <c r="D37">
-        <v>-132.626</v>
+        <v>-147.58799999999999</v>
       </c>
       <c r="E37">
-        <v>0.78383899999999995</v>
+        <v>0.79302499999999998</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2060,179 +2067,179 @@
         <v>58</v>
       </c>
       <c r="B38">
-        <v>1.6714500000000001</v>
+        <v>1.6896100000000001</v>
       </c>
       <c r="C38">
-        <v>-117.508</v>
+        <v>-117.581</v>
       </c>
       <c r="D38">
-        <v>-131.83099999999999</v>
+        <v>-132.626</v>
       </c>
       <c r="E38">
-        <v>0.77196399999999998</v>
+        <v>0.78383899999999995</v>
       </c>
       <c r="F38" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B39">
-        <v>1.606231</v>
+        <v>1.6714500000000001</v>
       </c>
       <c r="C39">
-        <v>-117.46299999999999</v>
+        <v>-117.508</v>
       </c>
       <c r="D39">
-        <v>-133.03200000000001</v>
+        <v>-131.83099999999999</v>
       </c>
       <c r="E39">
-        <v>0.73683600000000005</v>
+        <v>0.77196399999999998</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B40">
-        <v>1.6560790000000001</v>
+        <v>1.606231</v>
       </c>
       <c r="C40">
-        <v>-117.46</v>
+        <v>-117.46299999999999</v>
       </c>
       <c r="D40">
-        <v>-143.14599999999999</v>
+        <v>-133.03200000000001</v>
       </c>
       <c r="E40">
-        <v>0.769042</v>
+        <v>0.73683600000000005</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B41">
-        <v>1.6957089999999999</v>
+        <v>1.6560790000000001</v>
       </c>
       <c r="C41">
-        <v>-117.45399999999999</v>
+        <v>-117.46</v>
       </c>
       <c r="D41">
-        <v>-132.679</v>
+        <v>-143.14599999999999</v>
       </c>
       <c r="E41">
-        <v>0.78989399999999999</v>
+        <v>0.769042</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B42">
-        <v>1.5390219999999999</v>
+        <v>1.6957089999999999</v>
       </c>
       <c r="C42">
-        <v>-117.4</v>
+        <v>-117.45399999999999</v>
       </c>
       <c r="D42">
-        <v>-132.09</v>
+        <v>-132.679</v>
       </c>
       <c r="E42">
-        <v>0.70838900000000005</v>
+        <v>0.78989399999999999</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B43">
-        <v>1.6040270000000001</v>
+        <v>1.5390219999999999</v>
       </c>
       <c r="C43">
-        <v>-117.36499999999999</v>
+        <v>-117.4</v>
       </c>
       <c r="D43">
-        <v>-133.63800000000001</v>
+        <v>-132.09</v>
       </c>
       <c r="E43">
-        <v>0.745174</v>
+        <v>0.70838900000000005</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B44">
-        <v>1.6636740000000001</v>
+        <v>1.6040270000000001</v>
       </c>
       <c r="C44">
-        <v>-117.273</v>
+        <v>-117.36499999999999</v>
       </c>
       <c r="D44">
-        <v>-132.63</v>
+        <v>-133.63800000000001</v>
       </c>
       <c r="E44">
-        <v>0.77263000000000004</v>
+        <v>0.745174</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B45">
-        <v>1.7084090000000001</v>
+        <v>1.6636740000000001</v>
       </c>
       <c r="C45">
-        <v>-117.261</v>
+        <v>-117.273</v>
       </c>
       <c r="D45">
-        <v>-133.595</v>
+        <v>-132.63</v>
       </c>
       <c r="E45">
-        <v>0.79324799999999995</v>
+        <v>0.77263000000000004</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B46">
-        <v>1.7016260000000001</v>
+        <v>1.7084090000000001</v>
       </c>
       <c r="C46">
-        <v>-117.167</v>
+        <v>-117.261</v>
       </c>
       <c r="D46">
-        <v>-130.958</v>
+        <v>-133.595</v>
       </c>
       <c r="E46">
-        <v>0.78471199999999997</v>
+        <v>0.79324799999999995</v>
       </c>
       <c r="F46" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2240,16 +2247,16 @@
         <v>68</v>
       </c>
       <c r="B47">
-        <v>1.64821</v>
+        <v>1.7016260000000001</v>
       </c>
       <c r="C47">
-        <v>-117.108</v>
+        <v>-117.167</v>
       </c>
       <c r="D47">
-        <v>-130.58500000000001</v>
+        <v>-130.958</v>
       </c>
       <c r="E47">
-        <v>0.75765499999999997</v>
+        <v>0.78471199999999997</v>
       </c>
       <c r="F47" t="s">
         <v>69</v>
@@ -2260,16 +2267,16 @@
         <v>70</v>
       </c>
       <c r="B48">
-        <v>1.6165210000000001</v>
+        <v>1.64821</v>
       </c>
       <c r="C48">
-        <v>-117.06399999999999</v>
+        <v>-117.108</v>
       </c>
       <c r="D48">
-        <v>-133.304</v>
+        <v>-130.58500000000001</v>
       </c>
       <c r="E48">
-        <v>0.74495400000000001</v>
+        <v>0.75765499999999997</v>
       </c>
       <c r="F48" t="s">
         <v>71</v>
@@ -2280,45 +2287,44 @@
         <v>72</v>
       </c>
       <c r="B49">
-        <v>1.7089270000000001</v>
+        <v>1.6165210000000001</v>
       </c>
       <c r="C49">
-        <v>-117.032</v>
+        <v>-117.06399999999999</v>
       </c>
       <c r="D49">
-        <v>-133.52799999999999</v>
+        <v>-133.304</v>
       </c>
       <c r="E49">
-        <v>0.79191</v>
+        <v>0.74495400000000001</v>
       </c>
       <c r="F49" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B50">
-        <v>1.6531</v>
+        <v>1.7089270000000001</v>
       </c>
       <c r="C50">
-        <v>-117.024</v>
-      </c>
-      <c r="D50" t="e">
-        <f>-inf</f>
-        <v>#NAME?</v>
+        <v>-117.032</v>
+      </c>
+      <c r="D50">
+        <v>-133.52799999999999</v>
       </c>
       <c r="E50">
-        <v>0.76947699999999997</v>
+        <v>0.79191</v>
       </c>
       <c r="F50" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B51">
         <v>1.713533</v>
@@ -2333,12 +2339,12 @@
         <v>0.79057599999999995</v>
       </c>
       <c r="F51" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B52">
         <v>1.60991</v>
@@ -2353,12 +2359,12 @@
         <v>0.740066</v>
       </c>
       <c r="F52" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B53">
         <v>1.594436</v>
@@ -2373,12 +2379,12 @@
         <v>0.73694899999999997</v>
       </c>
       <c r="F53" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B54">
         <v>1.6802589999999999</v>
@@ -2393,12 +2399,12 @@
         <v>0.77367300000000006</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B55">
         <v>1.612323</v>
@@ -2413,12 +2419,12 @@
         <v>0.742259</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B56">
         <v>1.612619</v>
@@ -2433,12 +2439,12 @@
         <v>0.74408700000000005</v>
       </c>
       <c r="F56" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B57">
         <v>1.6672750000000001</v>
@@ -2453,12 +2459,12 @@
         <v>0.77339000000000002</v>
       </c>
       <c r="F57" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B58">
         <v>1.6036950000000001</v>
@@ -2473,12 +2479,12 @@
         <v>0.74124199999999996</v>
       </c>
       <c r="F58" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B59">
         <v>1.566004</v>
@@ -2493,12 +2499,12 @@
         <v>0.728518</v>
       </c>
       <c r="F59" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B60">
         <v>1.6533599999999999</v>
@@ -2513,12 +2519,12 @@
         <v>0.76183500000000004</v>
       </c>
       <c r="F60" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B61">
         <v>1.655278</v>
@@ -2538,7 +2544,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B62">
         <v>1.676385</v>
@@ -2553,12 +2559,12 @@
         <v>0.77735299999999996</v>
       </c>
       <c r="F62" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B63">
         <v>1.606989</v>
@@ -2573,12 +2579,12 @@
         <v>0.74315500000000001</v>
       </c>
       <c r="F63" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B64">
         <v>1.553471</v>
@@ -2593,12 +2599,12 @@
         <v>0.72587199999999996</v>
       </c>
       <c r="F64" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B65">
         <v>1.597559</v>
@@ -2613,12 +2619,12 @@
         <v>0.738367</v>
       </c>
       <c r="F65" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B66">
         <v>1.6750480000000001</v>
@@ -2633,12 +2639,12 @@
         <v>0.77514000000000005</v>
       </c>
       <c r="F66" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B67">
         <v>1.7189810000000001</v>
@@ -2653,12 +2659,12 @@
         <v>0.79583199999999998</v>
       </c>
       <c r="F67" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B68">
         <v>1.733495</v>
@@ -2673,12 +2679,12 @@
         <v>0.80384999999999995</v>
       </c>
       <c r="F68" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B69">
         <v>1.5833269999999999</v>
@@ -2693,12 +2699,12 @@
         <v>0.73289300000000002</v>
       </c>
       <c r="F69" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B70">
         <v>1.6557379999999999</v>
@@ -2713,12 +2719,12 @@
         <v>0.764015</v>
       </c>
       <c r="F70" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B71">
         <v>1.6491229999999999</v>
@@ -2733,12 +2739,12 @@
         <v>0.76182000000000005</v>
       </c>
       <c r="F71" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B72">
         <v>1.63592</v>
@@ -2753,12 +2759,12 @@
         <v>0.75345600000000001</v>
       </c>
       <c r="F72" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B73">
         <v>1.6536949999999999</v>
@@ -2773,12 +2779,12 @@
         <v>0.76889399999999997</v>
       </c>
       <c r="F73" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B74">
         <v>1.7435290000000001</v>
@@ -2793,12 +2799,12 @@
         <v>0.80769000000000002</v>
       </c>
       <c r="F74" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B75">
         <v>1.7191449999999999</v>
@@ -2813,12 +2819,12 @@
         <v>0.79775799999999997</v>
       </c>
       <c r="F75" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B76">
         <v>1.6521079999999999</v>
@@ -2833,12 +2839,12 @@
         <v>0.77258300000000002</v>
       </c>
       <c r="F76" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B77">
         <v>1.6045210000000001</v>
@@ -2853,12 +2859,12 @@
         <v>0.74199400000000004</v>
       </c>
       <c r="F77" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B78">
         <v>1.57331</v>
@@ -2873,12 +2879,12 @@
         <v>0.72712600000000005</v>
       </c>
       <c r="F78" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B79">
         <v>1.6051709999999999</v>
@@ -2893,12 +2899,12 @@
         <v>0.74231199999999997</v>
       </c>
       <c r="F79" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B80">
         <v>1.66221</v>
@@ -2913,12 +2919,12 @@
         <v>0.77320599999999995</v>
       </c>
       <c r="F80" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B81">
         <v>1.6695899999999999</v>
@@ -2933,12 +2939,12 @@
         <v>0.777223</v>
       </c>
       <c r="F81" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B82">
         <v>1.515126</v>
@@ -2953,12 +2959,12 @@
         <v>0.69583300000000003</v>
       </c>
       <c r="F82" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B83">
         <v>1.699058</v>
@@ -2973,12 +2979,12 @@
         <v>0.78742999999999996</v>
       </c>
       <c r="F83" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B84">
         <v>1.5971</v>
@@ -2993,12 +2999,12 @@
         <v>0.73522900000000002</v>
       </c>
       <c r="F84" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B85">
         <v>1.6373</v>
@@ -3013,12 +3019,12 @@
         <v>0.75105200000000005</v>
       </c>
       <c r="F85" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B86">
         <v>1.64066</v>
@@ -3033,12 +3039,12 @@
         <v>0.75841400000000003</v>
       </c>
       <c r="F86" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B87">
         <v>1.524834</v>
@@ -3058,7 +3064,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B88">
         <v>1.67073</v>
@@ -3073,12 +3079,12 @@
         <v>0.77317100000000005</v>
       </c>
       <c r="F88" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B89">
         <v>1.6505460000000001</v>
@@ -3093,12 +3099,12 @@
         <v>0.76571299999999998</v>
       </c>
       <c r="F89" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B90">
         <v>1.545617</v>
@@ -3113,12 +3119,12 @@
         <v>0.71626199999999995</v>
       </c>
       <c r="F90" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B91">
         <v>1.6711229999999999</v>
@@ -3133,12 +3139,12 @@
         <v>0.77685599999999999</v>
       </c>
       <c r="F91" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B92">
         <v>1.64533</v>
@@ -3153,12 +3159,12 @@
         <v>0.759189</v>
       </c>
       <c r="F92" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B93">
         <v>1.615696</v>
@@ -3173,12 +3179,12 @@
         <v>0.74496899999999999</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B94">
         <v>1.673983</v>
@@ -3193,12 +3199,12 @@
         <v>0.77517800000000003</v>
       </c>
       <c r="F94" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B95">
         <v>1.649821</v>
@@ -3213,12 +3219,12 @@
         <v>0.76111700000000004</v>
       </c>
       <c r="F95" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B96">
         <v>1.5009699999999999</v>
@@ -3233,12 +3239,12 @@
         <v>0.69155800000000001</v>
       </c>
       <c r="F96" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B97">
         <v>1.632053</v>
@@ -3253,12 +3259,12 @@
         <v>0.75595199999999996</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B98">
         <v>1.56664</v>
@@ -3273,12 +3279,12 @@
         <v>0.71922799999999998</v>
       </c>
       <c r="F98" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B99">
         <v>1.692364</v>
@@ -3293,12 +3299,12 @@
         <v>0.78590000000000004</v>
       </c>
       <c r="F99" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B100">
         <v>1.600231</v>
@@ -3313,12 +3319,12 @@
         <v>0.73787499999999995</v>
       </c>
       <c r="F100" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B101">
         <v>1.6315489999999999</v>
@@ -3333,12 +3339,12 @@
         <v>0.75582000000000005</v>
       </c>
       <c r="F101" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B102">
         <v>1.6284700000000001</v>
@@ -3353,12 +3359,12 @@
         <v>0.75585800000000003</v>
       </c>
       <c r="F102" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B103">
         <v>1.5892390000000001</v>
@@ -3373,12 +3379,12 @@
         <v>0.73343899999999995</v>
       </c>
       <c r="F103" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B104">
         <v>1.6765030000000001</v>
@@ -3393,12 +3399,12 @@
         <v>0.77987600000000001</v>
       </c>
       <c r="F104" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B105">
         <v>1.6253280000000001</v>
@@ -3413,12 +3419,12 @@
         <v>0.75134900000000004</v>
       </c>
       <c r="F105" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B106">
         <v>1.3818999999999999</v>
@@ -3433,12 +3439,12 @@
         <v>0.63164200000000004</v>
       </c>
       <c r="F106" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B107">
         <v>1.6183099999999999</v>
@@ -3453,12 +3459,12 @@
         <v>0.74597500000000005</v>
       </c>
       <c r="F107" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B108">
         <v>1.5690170000000001</v>
@@ -3473,12 +3479,12 @@
         <v>0.723499</v>
       </c>
       <c r="F108" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B109">
         <v>1.676301</v>
@@ -3493,12 +3499,12 @@
         <v>0.78463899999999998</v>
       </c>
       <c r="F109" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B110">
         <v>1.6843729999999999</v>
@@ -3518,7 +3524,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B111">
         <v>1.578667</v>
@@ -3533,12 +3539,12 @@
         <v>0.727854</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B112">
         <v>1.534205</v>
@@ -3558,7 +3564,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B113">
         <v>1.5228299999999999</v>
@@ -3573,12 +3579,12 @@
         <v>0.70538999999999996</v>
       </c>
       <c r="F113" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B114">
         <v>1.5021409999999999</v>
@@ -3593,12 +3599,12 @@
         <v>0.69493400000000005</v>
       </c>
       <c r="F114" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B115">
         <v>1.5861959999999999</v>
@@ -3613,7 +3619,7 @@
         <v>0.73500399999999999</v>
       </c>
       <c r="F115" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
